--- a/GestionAmbiental/wwwroot/ExcelTemplates/ResiduoSolido/JU-MAP-PRO-003-F002 CONTROL INGRESO Y SALIDA RESIDUOS SÓLIDOS ACR O CMRS.xlsx
+++ b/GestionAmbiental/wwwroot/ExcelTemplates/ResiduoSolido/JU-MAP-PRO-003-F002 CONTROL INGRESO Y SALIDA RESIDUOS SÓLIDOS ACR O CMRS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electrodata\Marcobre\Tablas Maestras\Marcobre-GestionAmbiental\GestionAmbiental\wwwroot\ExcelTemplates\ResiduoSolido\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA45A94-2D31-4DB0-881B-8EA557312894}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97098ED-1271-4F55-A8EA-166895CB1937}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5880" yWindow="4215" windowWidth="21600" windowHeight="11385" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATOS" sheetId="4" state="hidden" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="218">
   <si>
     <t>ITEM</t>
   </si>
@@ -50,9 +50,6 @@
     <t>TIPO DE RESIDUO</t>
   </si>
   <si>
-    <t>Papel y cartón</t>
-  </si>
-  <si>
     <t>EMPRESA QUE GENERÓ/RETIRÓ EL RESIDUO</t>
   </si>
   <si>
@@ -60,12 +57,6 @@
   </si>
   <si>
     <t>MOTIVO DE INGRESO O SALIDA DE RESIDUOS</t>
-  </si>
-  <si>
-    <t>Almacenamiento Temporal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disposición Final </t>
   </si>
   <si>
     <t>COMENTARIOS
@@ -703,7 +694,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -733,12 +724,6 @@
       <b/>
       <sz val="8"/>
       <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1023,12 +1008,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1040,16 +1025,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1058,32 +1033,53 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1132,27 +1128,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1641,58 +1616,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="C1" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>215</v>
+      <c r="C1" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A2" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>216</v>
+      <c r="A2" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="D2" s="2">
         <v>98925</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>218</v>
+      <c r="F2" s="4" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>217</v>
+      <c r="A3" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="D3" s="2">
         <v>208575</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>219</v>
+      <c r="F3" s="4" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="C4" s="8" t="s">
-        <v>213</v>
+      <c r="C4" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="D4" s="2">
         <v>93951</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>58</v>
+      <c r="A5" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>57</v>
+      <c r="A6" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -1700,240 +1675,240 @@
       <c r="D7" s="2"/>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="W8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="X8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AD8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AF8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AG8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AI8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AJ8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AK8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="AM8" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" s="6" customFormat="1" ht="96" x14ac:dyDescent="0.2">
+      <c r="B9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="V9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W9" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="X9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA9" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC9" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AF9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG9" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="AI9" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="AK9" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AL9" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="AM9" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="R8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="S8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="T8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="U8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="W8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="X8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE8" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF8" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG8" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH8" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI8" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AJ8" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AK8" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AL8" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="AM8" s="19" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:39" s="10" customFormat="1" ht="96" x14ac:dyDescent="0.2">
-      <c r="B9" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q9" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="R9" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="S9" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="T9" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="U9" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="V9" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="W9" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="X9" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y9" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z9" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA9" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB9" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC9" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD9" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="AE9" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="AF9" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG9" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH9" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI9" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ9" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK9" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="AL9" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="AM9" s="17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="B10" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -2089,8 +2064,8 @@
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
-        <v>61</v>
+      <c r="A11" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -2246,8 +2221,8 @@
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A12" s="8" t="s">
-        <v>62</v>
+      <c r="A12" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -2403,8 +2378,8 @@
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
-        <v>63</v>
+      <c r="A13" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -2560,8 +2535,8 @@
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A14" s="8" t="s">
-        <v>64</v>
+      <c r="A14" s="4" t="s">
+        <v>61</v>
       </c>
       <c r="B14" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -2717,8 +2692,8 @@
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A15" s="8" t="s">
-        <v>65</v>
+      <c r="A15" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -2874,8 +2849,8 @@
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>66</v>
+      <c r="A16" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="B16" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -3031,8 +3006,8 @@
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
-        <v>67</v>
+      <c r="A17" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="B17" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -3188,8 +3163,8 @@
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A18" s="8" t="s">
-        <v>68</v>
+      <c r="A18" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="B18" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -3345,8 +3320,8 @@
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
-        <v>69</v>
+      <c r="A19" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="B19" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -3502,8 +3477,8 @@
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A20" s="8" t="s">
-        <v>70</v>
+      <c r="A20" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="B20" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -3659,8 +3634,8 @@
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A21" s="8" t="s">
-        <v>71</v>
+      <c r="A21" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="B21" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -3816,8 +3791,8 @@
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A22" s="8" t="s">
-        <v>72</v>
+      <c r="A22" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="B22" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -3973,8 +3948,8 @@
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A23" s="8" t="s">
-        <v>73</v>
+      <c r="A23" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="B23" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -4130,8 +4105,8 @@
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A24" s="8" t="s">
-        <v>74</v>
+      <c r="A24" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="B24" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -4287,8 +4262,8 @@
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A25" s="8" t="s">
-        <v>75</v>
+      <c r="A25" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="B25" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -4444,8 +4419,8 @@
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A26" s="8" t="s">
-        <v>76</v>
+      <c r="A26" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="B26" s="2" t="e">
         <f>IF('F002'!#REF!="PELIGROSO",DATOS!$B$9,"")</f>
@@ -4601,328 +4576,328 @@
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A27" s="8"/>
+      <c r="A27" s="4"/>
       <c r="D27" s="2"/>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A28" s="8"/>
+      <c r="A28" s="4"/>
       <c r="D28" s="2"/>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
+      <c r="A29" s="4"/>
       <c r="D29" s="2"/>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A30" s="8"/>
+      <c r="A30" s="4"/>
       <c r="D30" s="2"/>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A31" s="8"/>
+      <c r="A31" s="4"/>
       <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A32" s="8"/>
+      <c r="A32" s="4"/>
       <c r="D32" s="2"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="8"/>
+      <c r="A33" s="4"/>
       <c r="D33" s="2"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="8"/>
+      <c r="A34" s="4"/>
       <c r="D34" s="2"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="8"/>
+      <c r="A35" s="4"/>
       <c r="D35" s="2"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="8"/>
+      <c r="A36" s="4"/>
       <c r="D36" s="2"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="8"/>
+      <c r="A37" s="4"/>
       <c r="D37" s="2"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="8"/>
+      <c r="A38" s="4"/>
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="8"/>
+      <c r="A39" s="4"/>
       <c r="D39" s="2"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="8"/>
+      <c r="A40" s="4"/>
       <c r="D40" s="2"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="8"/>
+      <c r="A41" s="4"/>
       <c r="D41" s="2"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="8"/>
+      <c r="A42" s="4"/>
       <c r="D42" s="2"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="8"/>
+      <c r="A43" s="4"/>
       <c r="D43" s="2"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="8"/>
+      <c r="A44" s="4"/>
       <c r="D44" s="2"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="8"/>
+      <c r="A45" s="4"/>
       <c r="D45" s="2"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="8"/>
+      <c r="A46" s="4"/>
       <c r="D46" s="2"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="8"/>
+      <c r="A47" s="4"/>
       <c r="D47" s="2"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="8"/>
+      <c r="A48" s="4"/>
       <c r="D48" s="2"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="8"/>
+      <c r="A49" s="4"/>
       <c r="D49" s="2"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="8"/>
+      <c r="A50" s="4"/>
       <c r="D50" s="2"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="8"/>
+      <c r="A51" s="4"/>
       <c r="D51" s="2"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="8"/>
+      <c r="A52" s="4"/>
       <c r="D52" s="2"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="8"/>
+      <c r="A53" s="4"/>
       <c r="D53" s="2"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="8"/>
+      <c r="A54" s="4"/>
       <c r="D54" s="2"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="8"/>
+      <c r="A55" s="4"/>
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="8"/>
+      <c r="A56" s="4"/>
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="8"/>
+      <c r="A57" s="4"/>
       <c r="D57" s="2"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="8"/>
+      <c r="A58" s="4"/>
       <c r="D58" s="2"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="8"/>
+      <c r="A59" s="4"/>
       <c r="D59" s="2"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="8"/>
+      <c r="A60" s="4"/>
       <c r="D60" s="2"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="8"/>
+      <c r="A61" s="4"/>
       <c r="D61" s="2"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="8"/>
+      <c r="A62" s="4"/>
       <c r="D62" s="2"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="8"/>
+      <c r="A63" s="4"/>
       <c r="D63" s="2"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="8"/>
+      <c r="A64" s="4"/>
       <c r="D64" s="2"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="8"/>
+      <c r="A65" s="4"/>
       <c r="D65" s="2"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="8"/>
+      <c r="A66" s="4"/>
       <c r="D66" s="2"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="8"/>
+      <c r="A67" s="4"/>
       <c r="D67" s="2"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="8"/>
+      <c r="A68" s="4"/>
       <c r="D68" s="2"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="8"/>
+      <c r="A69" s="4"/>
       <c r="D69" s="2"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="8"/>
+      <c r="A70" s="4"/>
       <c r="D70" s="2"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="8"/>
+      <c r="A71" s="4"/>
       <c r="D71" s="2"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="8"/>
+      <c r="A72" s="4"/>
       <c r="D72" s="2"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="8"/>
+      <c r="A73" s="4"/>
       <c r="D73" s="2"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="8"/>
+      <c r="A74" s="4"/>
       <c r="D74" s="2"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="8"/>
+      <c r="A75" s="4"/>
       <c r="D75" s="2"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="8"/>
+      <c r="A76" s="4"/>
       <c r="D76" s="2"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="8"/>
+      <c r="A77" s="4"/>
       <c r="D77" s="2"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="8"/>
+      <c r="A78" s="4"/>
       <c r="D78" s="2"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="8"/>
+      <c r="A79" s="4"/>
       <c r="D79" s="2"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="8"/>
+      <c r="A80" s="4"/>
       <c r="D80" s="2"/>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="8"/>
+      <c r="A81" s="4"/>
       <c r="D81" s="2"/>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="8"/>
+      <c r="A82" s="4"/>
       <c r="D82" s="2"/>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="8"/>
+      <c r="A83" s="4"/>
       <c r="D83" s="2"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="8"/>
+      <c r="A84" s="4"/>
       <c r="D84" s="2"/>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="8"/>
+      <c r="A85" s="4"/>
       <c r="D85" s="2"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="8"/>
+      <c r="A86" s="4"/>
       <c r="D86" s="2"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="8"/>
+      <c r="A87" s="4"/>
       <c r="D87" s="2"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="8"/>
+      <c r="A88" s="4"/>
       <c r="D88" s="2"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="8"/>
+      <c r="A89" s="4"/>
       <c r="D89" s="2"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="8"/>
+      <c r="A90" s="4"/>
       <c r="D90" s="2"/>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="8"/>
+      <c r="A91" s="4"/>
       <c r="D91" s="2"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="8"/>
+      <c r="A92" s="4"/>
       <c r="D92" s="2"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="8"/>
+      <c r="A93" s="4"/>
       <c r="D93" s="2"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="8"/>
+      <c r="A94" s="4"/>
       <c r="D94" s="2"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="8"/>
+      <c r="A95" s="4"/>
       <c r="D95" s="2"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="8"/>
+      <c r="A96" s="4"/>
       <c r="D96" s="2"/>
     </row>
     <row r="97" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A97" s="8"/>
+      <c r="A97" s="4"/>
       <c r="D97" s="2"/>
     </row>
     <row r="98" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A98" s="8"/>
+      <c r="A98" s="4"/>
       <c r="D98" s="2"/>
     </row>
     <row r="99" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A99" s="8"/>
+      <c r="A99" s="4"/>
       <c r="D99" s="2"/>
     </row>
     <row r="100" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A100" s="8"/>
+      <c r="A100" s="4"/>
       <c r="D100" s="2"/>
     </row>
     <row r="101" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A101" s="8"/>
+      <c r="A101" s="4"/>
       <c r="D101" s="2"/>
     </row>
     <row r="102" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A102" s="8"/>
+      <c r="A102" s="4"/>
       <c r="D102" s="2"/>
     </row>
     <row r="103" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A103" s="8"/>
+      <c r="A103" s="4"/>
       <c r="D103" s="2"/>
     </row>
     <row r="104" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A104" s="8"/>
+      <c r="A104" s="4"/>
       <c r="D104" s="2"/>
     </row>
     <row r="105" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A105" s="8"/>
+      <c r="A105" s="4"/>
       <c r="D105" s="2"/>
     </row>
     <row r="106" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A106" s="8"/>
+      <c r="A106" s="4"/>
       <c r="D106" s="2"/>
     </row>
     <row r="107" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A107" s="8" t="s">
-        <v>77</v>
+      <c r="A107" s="4" t="s">
+        <v>74</v>
       </c>
       <c r="B107" s="2" t="str">
         <f>IF('F002'!$G10="PELIGROSO",DATOS!$B$9,"")</f>
@@ -5078,8 +5053,8 @@
       </c>
     </row>
     <row r="108" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A108" s="8" t="s">
-        <v>78</v>
+      <c r="A108" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="B108" s="2" t="str">
         <f>IF('F002'!$G11="PELIGROSO",DATOS!$B$9,"")</f>
@@ -5235,8 +5210,8 @@
       </c>
     </row>
     <row r="109" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A109" s="8" t="s">
-        <v>79</v>
+      <c r="A109" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="B109" s="2" t="str">
         <f>IF('F002'!$G12="PELIGROSO",DATOS!$B$9,"")</f>
@@ -5392,8 +5367,8 @@
       </c>
     </row>
     <row r="110" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A110" s="8" t="s">
-        <v>80</v>
+      <c r="A110" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="B110" s="2" t="str">
         <f>IF('F002'!$G13="PELIGROSO",DATOS!$B$9,"")</f>
@@ -5549,8 +5524,8 @@
       </c>
     </row>
     <row r="111" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A111" s="8" t="s">
-        <v>81</v>
+      <c r="A111" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="B111" s="2" t="str">
         <f>IF('F002'!$G14="PELIGROSO",DATOS!$B$9,"")</f>
@@ -5706,8 +5681,8 @@
       </c>
     </row>
     <row r="112" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A112" s="8" t="s">
-        <v>82</v>
+      <c r="A112" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="B112" s="2" t="str">
         <f>IF('F002'!$G15="PELIGROSO",DATOS!$B$9,"")</f>
@@ -5863,8 +5838,8 @@
       </c>
     </row>
     <row r="113" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A113" s="8" t="s">
-        <v>83</v>
+      <c r="A113" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="B113" s="2" t="str">
         <f>IF('F002'!$G16="PELIGROSO",DATOS!$B$9,"")</f>
@@ -6020,8 +5995,8 @@
       </c>
     </row>
     <row r="114" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A114" s="8" t="s">
-        <v>84</v>
+      <c r="A114" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="B114" s="2" t="str">
         <f>IF('F002'!$G17="PELIGROSO",DATOS!$B$9,"")</f>
@@ -6177,8 +6152,8 @@
       </c>
     </row>
     <row r="115" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A115" s="8" t="s">
-        <v>85</v>
+      <c r="A115" s="4" t="s">
+        <v>82</v>
       </c>
       <c r="B115" s="2" t="str">
         <f>IF('F002'!$G18="PELIGROSO",DATOS!$B$9,"")</f>
@@ -6334,8 +6309,8 @@
       </c>
     </row>
     <row r="116" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A116" s="8" t="s">
-        <v>86</v>
+      <c r="A116" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="AF116" s="2" t="str">
         <f>IF('F002'!$G19="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6371,8 +6346,8 @@
       </c>
     </row>
     <row r="117" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A117" s="8" t="s">
-        <v>87</v>
+      <c r="A117" s="4" t="s">
+        <v>84</v>
       </c>
       <c r="AF117" s="2" t="str">
         <f>IF('F002'!$G20="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6408,8 +6383,8 @@
       </c>
     </row>
     <row r="118" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A118" s="8" t="s">
-        <v>88</v>
+      <c r="A118" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="AF118" s="2" t="str">
         <f>IF('F002'!$G21="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6445,8 +6420,8 @@
       </c>
     </row>
     <row r="119" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A119" s="8" t="s">
-        <v>89</v>
+      <c r="A119" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="AF119" s="2" t="str">
         <f>IF('F002'!$G22="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6482,8 +6457,8 @@
       </c>
     </row>
     <row r="120" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A120" s="8" t="s">
-        <v>90</v>
+      <c r="A120" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="AF120" s="2" t="str">
         <f>IF('F002'!$G23="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6519,8 +6494,8 @@
       </c>
     </row>
     <row r="121" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A121" s="8" t="s">
-        <v>91</v>
+      <c r="A121" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="AF121" s="2" t="str">
         <f>IF('F002'!$G24="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6556,8 +6531,8 @@
       </c>
     </row>
     <row r="122" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A122" s="8" t="s">
-        <v>92</v>
+      <c r="A122" s="4" t="s">
+        <v>89</v>
       </c>
       <c r="AF122" s="2" t="str">
         <f>IF('F002'!$G25="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6593,8 +6568,8 @@
       </c>
     </row>
     <row r="123" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A123" s="8" t="s">
-        <v>93</v>
+      <c r="A123" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="AF123" s="2" t="str">
         <f>IF('F002'!$G26="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6630,8 +6605,8 @@
       </c>
     </row>
     <row r="124" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A124" s="8" t="s">
-        <v>94</v>
+      <c r="A124" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="AF124" s="2" t="str">
         <f>IF('F002'!$G27="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6667,8 +6642,8 @@
       </c>
     </row>
     <row r="125" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A125" s="8" t="s">
-        <v>95</v>
+      <c r="A125" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="AF125" s="2" t="str">
         <f>IF('F002'!$G28="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6704,8 +6679,8 @@
       </c>
     </row>
     <row r="126" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A126" s="8" t="s">
-        <v>96</v>
+      <c r="A126" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="AF126" s="2" t="str">
         <f>IF('F002'!$G29="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6741,8 +6716,8 @@
       </c>
     </row>
     <row r="127" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A127" s="8" t="s">
-        <v>97</v>
+      <c r="A127" s="4" t="s">
+        <v>94</v>
       </c>
       <c r="AF127" s="2" t="str">
         <f>IF('F002'!$G30="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6778,8 +6753,8 @@
       </c>
     </row>
     <row r="128" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A128" s="8" t="s">
-        <v>98</v>
+      <c r="A128" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="AF128" s="2" t="str">
         <f>IF('F002'!$G31="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6815,8 +6790,8 @@
       </c>
     </row>
     <row r="129" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A129" s="8" t="s">
-        <v>99</v>
+      <c r="A129" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="AF129" s="2" t="str">
         <f>IF('F002'!$G32="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6852,8 +6827,8 @@
       </c>
     </row>
     <row r="130" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A130" s="8" t="s">
-        <v>100</v>
+      <c r="A130" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="AF130" s="2" t="str">
         <f>IF('F002'!$G33="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6889,8 +6864,8 @@
       </c>
     </row>
     <row r="131" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A131" s="8" t="s">
-        <v>101</v>
+      <c r="A131" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="AF131" s="2" t="str">
         <f>IF('F002'!$G34="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6926,8 +6901,8 @@
       </c>
     </row>
     <row r="132" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A132" s="8" t="s">
-        <v>102</v>
+      <c r="A132" s="4" t="s">
+        <v>99</v>
       </c>
       <c r="AF132" s="2" t="str">
         <f>IF('F002'!$G35="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -6963,8 +6938,8 @@
       </c>
     </row>
     <row r="133" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A133" s="8" t="s">
-        <v>103</v>
+      <c r="A133" s="4" t="s">
+        <v>100</v>
       </c>
       <c r="AF133" s="2" t="str">
         <f>IF('F002'!$G36="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7000,8 +6975,8 @@
       </c>
     </row>
     <row r="134" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A134" s="8" t="s">
-        <v>104</v>
+      <c r="A134" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="AF134" s="2" t="str">
         <f>IF('F002'!$G37="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7037,8 +7012,8 @@
       </c>
     </row>
     <row r="135" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A135" s="8" t="s">
-        <v>105</v>
+      <c r="A135" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="AF135" s="2" t="str">
         <f>IF('F002'!$G38="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7074,8 +7049,8 @@
       </c>
     </row>
     <row r="136" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A136" s="8" t="s">
-        <v>106</v>
+      <c r="A136" s="4" t="s">
+        <v>103</v>
       </c>
       <c r="AF136" s="2" t="str">
         <f>IF('F002'!$G39="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7111,8 +7086,8 @@
       </c>
     </row>
     <row r="137" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A137" s="8" t="s">
-        <v>107</v>
+      <c r="A137" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="AF137" s="2" t="str">
         <f>IF('F002'!$G40="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7148,8 +7123,8 @@
       </c>
     </row>
     <row r="138" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A138" s="8" t="s">
-        <v>108</v>
+      <c r="A138" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="AF138" s="2" t="str">
         <f>IF('F002'!$G41="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7185,8 +7160,8 @@
       </c>
     </row>
     <row r="139" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A139" s="8" t="s">
-        <v>109</v>
+      <c r="A139" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="AF139" s="2" t="str">
         <f>IF('F002'!$G42="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7222,8 +7197,8 @@
       </c>
     </row>
     <row r="140" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A140" s="8" t="s">
-        <v>110</v>
+      <c r="A140" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="AF140" s="2" t="str">
         <f>IF('F002'!$G43="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7259,8 +7234,8 @@
       </c>
     </row>
     <row r="141" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A141" s="8" t="s">
-        <v>111</v>
+      <c r="A141" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="AF141" s="2" t="str">
         <f>IF('F002'!$G44="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7296,8 +7271,8 @@
       </c>
     </row>
     <row r="142" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A142" s="8" t="s">
-        <v>112</v>
+      <c r="A142" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="AF142" s="2" t="str">
         <f>IF('F002'!$G45="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7333,8 +7308,8 @@
       </c>
     </row>
     <row r="143" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A143" s="8" t="s">
-        <v>113</v>
+      <c r="A143" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="AF143" s="2" t="str">
         <f>IF('F002'!$G46="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7370,8 +7345,8 @@
       </c>
     </row>
     <row r="144" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A144" s="8" t="s">
-        <v>114</v>
+      <c r="A144" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="AF144" s="2" t="str">
         <f>IF('F002'!$G47="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7407,8 +7382,8 @@
       </c>
     </row>
     <row r="145" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A145" s="8" t="s">
-        <v>115</v>
+      <c r="A145" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="AF145" s="2" t="str">
         <f>IF('F002'!$G48="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7444,8 +7419,8 @@
       </c>
     </row>
     <row r="146" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A146" s="8" t="s">
-        <v>116</v>
+      <c r="A146" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="AF146" s="2" t="str">
         <f>IF('F002'!$G49="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7481,8 +7456,8 @@
       </c>
     </row>
     <row r="147" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A147" s="8" t="s">
-        <v>117</v>
+      <c r="A147" s="4" t="s">
+        <v>114</v>
       </c>
       <c r="AF147" s="2" t="str">
         <f>IF('F002'!$G50="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7518,8 +7493,8 @@
       </c>
     </row>
     <row r="148" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A148" s="8" t="s">
-        <v>118</v>
+      <c r="A148" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="AF148" s="2" t="str">
         <f>IF('F002'!$G51="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7555,8 +7530,8 @@
       </c>
     </row>
     <row r="149" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A149" s="8" t="s">
-        <v>119</v>
+      <c r="A149" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="AF149" s="2" t="str">
         <f>IF('F002'!$G52="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7592,8 +7567,8 @@
       </c>
     </row>
     <row r="150" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A150" s="8" t="s">
-        <v>120</v>
+      <c r="A150" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="AF150" s="2" t="str">
         <f>IF('F002'!$G53="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7629,8 +7604,8 @@
       </c>
     </row>
     <row r="151" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A151" s="8" t="s">
-        <v>121</v>
+      <c r="A151" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="AF151" s="2" t="str">
         <f>IF('F002'!$G54="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7666,8 +7641,8 @@
       </c>
     </row>
     <row r="152" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A152" s="8" t="s">
-        <v>122</v>
+      <c r="A152" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="AF152" s="2" t="str">
         <f>IF('F002'!$G55="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7703,8 +7678,8 @@
       </c>
     </row>
     <row r="153" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A153" s="8" t="s">
-        <v>123</v>
+      <c r="A153" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="AF153" s="2" t="str">
         <f>IF('F002'!$G56="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7740,8 +7715,8 @@
       </c>
     </row>
     <row r="154" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A154" s="8" t="s">
-        <v>124</v>
+      <c r="A154" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="AF154" s="2" t="str">
         <f>IF('F002'!$G57="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7777,8 +7752,8 @@
       </c>
     </row>
     <row r="155" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A155" s="8" t="s">
-        <v>125</v>
+      <c r="A155" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="AF155" s="2" t="str">
         <f>IF('F002'!$G58="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7814,8 +7789,8 @@
       </c>
     </row>
     <row r="156" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A156" s="8" t="s">
-        <v>126</v>
+      <c r="A156" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="AF156" s="2" t="str">
         <f>IF('F002'!$G59="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7851,8 +7826,8 @@
       </c>
     </row>
     <row r="157" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A157" s="8" t="s">
-        <v>127</v>
+      <c r="A157" s="4" t="s">
+        <v>124</v>
       </c>
       <c r="AF157" s="2" t="str">
         <f>IF('F002'!$G60="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7888,8 +7863,8 @@
       </c>
     </row>
     <row r="158" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A158" s="8" t="s">
-        <v>128</v>
+      <c r="A158" s="4" t="s">
+        <v>125</v>
       </c>
       <c r="AF158" s="2" t="str">
         <f>IF('F002'!$G61="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7925,8 +7900,8 @@
       </c>
     </row>
     <row r="159" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A159" s="8" t="s">
-        <v>129</v>
+      <c r="A159" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="AF159" s="2" t="str">
         <f>IF('F002'!$G62="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7962,8 +7937,8 @@
       </c>
     </row>
     <row r="160" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A160" s="8" t="s">
-        <v>130</v>
+      <c r="A160" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="AF160" s="2" t="str">
         <f>IF('F002'!$G63="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -7999,8 +7974,8 @@
       </c>
     </row>
     <row r="161" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A161" s="8" t="s">
-        <v>131</v>
+      <c r="A161" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="AF161" s="2" t="str">
         <f>IF('F002'!$G64="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8036,8 +8011,8 @@
       </c>
     </row>
     <row r="162" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A162" s="8" t="s">
-        <v>132</v>
+      <c r="A162" s="4" t="s">
+        <v>129</v>
       </c>
       <c r="AF162" s="2" t="str">
         <f>IF('F002'!$G65="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8073,8 +8048,8 @@
       </c>
     </row>
     <row r="163" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A163" s="8" t="s">
-        <v>133</v>
+      <c r="A163" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="AF163" s="2" t="str">
         <f>IF('F002'!$G66="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8110,8 +8085,8 @@
       </c>
     </row>
     <row r="164" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A164" s="8" t="s">
-        <v>134</v>
+      <c r="A164" s="4" t="s">
+        <v>131</v>
       </c>
       <c r="AF164" s="2" t="str">
         <f>IF('F002'!$G67="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8147,8 +8122,8 @@
       </c>
     </row>
     <row r="165" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A165" s="8" t="s">
-        <v>135</v>
+      <c r="A165" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="AF165" s="2" t="str">
         <f>IF('F002'!$G68="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8184,8 +8159,8 @@
       </c>
     </row>
     <row r="166" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A166" s="8" t="s">
-        <v>136</v>
+      <c r="A166" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="AF166" s="2" t="str">
         <f>IF('F002'!$G69="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8221,8 +8196,8 @@
       </c>
     </row>
     <row r="167" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A167" s="8" t="s">
-        <v>137</v>
+      <c r="A167" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="AF167" s="2" t="str">
         <f>IF('F002'!$G70="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8258,8 +8233,8 @@
       </c>
     </row>
     <row r="168" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A168" s="8" t="s">
-        <v>138</v>
+      <c r="A168" s="4" t="s">
+        <v>135</v>
       </c>
       <c r="AF168" s="2" t="str">
         <f>IF('F002'!$G71="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8295,8 +8270,8 @@
       </c>
     </row>
     <row r="169" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A169" s="8" t="s">
-        <v>139</v>
+      <c r="A169" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="AF169" s="2" t="str">
         <f>IF('F002'!$G72="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8332,8 +8307,8 @@
       </c>
     </row>
     <row r="170" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A170" s="8" t="s">
-        <v>140</v>
+      <c r="A170" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="AF170" s="2" t="str">
         <f>IF('F002'!$G73="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8369,8 +8344,8 @@
       </c>
     </row>
     <row r="171" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A171" s="8" t="s">
-        <v>141</v>
+      <c r="A171" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="AF171" s="2" t="str">
         <f>IF('F002'!$G74="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8406,8 +8381,8 @@
       </c>
     </row>
     <row r="172" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A172" s="8" t="s">
-        <v>142</v>
+      <c r="A172" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="AF172" s="2" t="str">
         <f>IF('F002'!$G75="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8443,8 +8418,8 @@
       </c>
     </row>
     <row r="173" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A173" s="8" t="s">
-        <v>143</v>
+      <c r="A173" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="AF173" s="2" t="str">
         <f>IF('F002'!$G76="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8480,8 +8455,8 @@
       </c>
     </row>
     <row r="174" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A174" s="8" t="s">
-        <v>144</v>
+      <c r="A174" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="AF174" s="2" t="str">
         <f>IF('F002'!$G77="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8517,8 +8492,8 @@
       </c>
     </row>
     <row r="175" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A175" s="8" t="s">
-        <v>145</v>
+      <c r="A175" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="AF175" s="2" t="str">
         <f>IF('F002'!$G78="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8554,8 +8529,8 @@
       </c>
     </row>
     <row r="176" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A176" s="8" t="s">
-        <v>146</v>
+      <c r="A176" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="AF176" s="2" t="str">
         <f>IF('F002'!$G79="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8591,8 +8566,8 @@
       </c>
     </row>
     <row r="177" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A177" s="8" t="s">
-        <v>147</v>
+      <c r="A177" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="AF177" s="2" t="str">
         <f>IF('F002'!$G80="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8628,8 +8603,8 @@
       </c>
     </row>
     <row r="178" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A178" s="8" t="s">
-        <v>148</v>
+      <c r="A178" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="AF178" s="2" t="str">
         <f>IF('F002'!$G81="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8665,8 +8640,8 @@
       </c>
     </row>
     <row r="179" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A179" s="8" t="s">
-        <v>149</v>
+      <c r="A179" s="4" t="s">
+        <v>146</v>
       </c>
       <c r="AF179" s="2" t="str">
         <f>IF('F002'!$G82="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8702,8 +8677,8 @@
       </c>
     </row>
     <row r="180" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A180" s="8" t="s">
-        <v>150</v>
+      <c r="A180" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="AF180" s="2" t="str">
         <f>IF('F002'!$G83="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8739,8 +8714,8 @@
       </c>
     </row>
     <row r="181" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A181" s="8" t="s">
-        <v>151</v>
+      <c r="A181" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="AF181" s="2" t="str">
         <f>IF('F002'!$G84="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8776,8 +8751,8 @@
       </c>
     </row>
     <row r="182" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A182" s="8" t="s">
-        <v>152</v>
+      <c r="A182" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="AF182" s="2" t="str">
         <f>IF('F002'!$G85="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8813,8 +8788,8 @@
       </c>
     </row>
     <row r="183" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A183" s="8" t="s">
-        <v>153</v>
+      <c r="A183" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="AF183" s="2" t="str">
         <f>IF('F002'!$G86="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8850,8 +8825,8 @@
       </c>
     </row>
     <row r="184" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A184" s="8" t="s">
-        <v>154</v>
+      <c r="A184" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="AF184" s="2" t="str">
         <f>IF('F002'!$G87="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8887,8 +8862,8 @@
       </c>
     </row>
     <row r="185" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A185" s="8" t="s">
-        <v>155</v>
+      <c r="A185" s="4" t="s">
+        <v>152</v>
       </c>
       <c r="AF185" s="2" t="str">
         <f>IF('F002'!$G88="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8924,8 +8899,8 @@
       </c>
     </row>
     <row r="186" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A186" s="8" t="s">
-        <v>156</v>
+      <c r="A186" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="AF186" s="2" t="str">
         <f>IF('F002'!$G89="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8961,8 +8936,8 @@
       </c>
     </row>
     <row r="187" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A187" s="8" t="s">
-        <v>157</v>
+      <c r="A187" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="AF187" s="2" t="str">
         <f>IF('F002'!$G90="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -8998,8 +8973,8 @@
       </c>
     </row>
     <row r="188" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A188" s="8" t="s">
-        <v>158</v>
+      <c r="A188" s="4" t="s">
+        <v>155</v>
       </c>
       <c r="AF188" s="2" t="str">
         <f>IF('F002'!$G91="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9035,8 +9010,8 @@
       </c>
     </row>
     <row r="189" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A189" s="8" t="s">
-        <v>159</v>
+      <c r="A189" s="4" t="s">
+        <v>156</v>
       </c>
       <c r="AF189" s="2" t="str">
         <f>IF('F002'!$G92="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9072,8 +9047,8 @@
       </c>
     </row>
     <row r="190" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A190" s="8" t="s">
-        <v>160</v>
+      <c r="A190" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="AF190" s="2" t="str">
         <f>IF('F002'!$G93="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9109,8 +9084,8 @@
       </c>
     </row>
     <row r="191" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A191" s="8" t="s">
-        <v>161</v>
+      <c r="A191" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="AF191" s="2" t="str">
         <f>IF('F002'!$G94="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9146,8 +9121,8 @@
       </c>
     </row>
     <row r="192" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A192" s="8" t="s">
-        <v>162</v>
+      <c r="A192" s="4" t="s">
+        <v>159</v>
       </c>
       <c r="AF192" s="2" t="str">
         <f>IF('F002'!$G95="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9183,8 +9158,8 @@
       </c>
     </row>
     <row r="193" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A193" s="8" t="s">
-        <v>163</v>
+      <c r="A193" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="AF193" s="2" t="str">
         <f>IF('F002'!$G96="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9220,8 +9195,8 @@
       </c>
     </row>
     <row r="194" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A194" s="8" t="s">
-        <v>164</v>
+      <c r="A194" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="AF194" s="2" t="str">
         <f>IF('F002'!$G97="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9257,8 +9232,8 @@
       </c>
     </row>
     <row r="195" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A195" s="8" t="s">
-        <v>165</v>
+      <c r="A195" s="4" t="s">
+        <v>162</v>
       </c>
       <c r="AF195" s="2" t="str">
         <f>IF('F002'!$G98="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9294,8 +9269,8 @@
       </c>
     </row>
     <row r="196" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A196" s="8" t="s">
-        <v>166</v>
+      <c r="A196" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="AF196" s="2" t="str">
         <f>IF('F002'!$G99="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9331,8 +9306,8 @@
       </c>
     </row>
     <row r="197" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A197" s="8" t="s">
-        <v>167</v>
+      <c r="A197" s="4" t="s">
+        <v>164</v>
       </c>
       <c r="AF197" s="2" t="str">
         <f>IF('F002'!$G100="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9368,8 +9343,8 @@
       </c>
     </row>
     <row r="198" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A198" s="8" t="s">
-        <v>168</v>
+      <c r="A198" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="AF198" s="2" t="str">
         <f>IF('F002'!$G101="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9405,8 +9380,8 @@
       </c>
     </row>
     <row r="199" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A199" s="8" t="s">
-        <v>169</v>
+      <c r="A199" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="AF199" s="2" t="str">
         <f>IF('F002'!$G102="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9442,8 +9417,8 @@
       </c>
     </row>
     <row r="200" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A200" s="8" t="s">
-        <v>170</v>
+      <c r="A200" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="AF200" s="2" t="str">
         <f>IF('F002'!$G103="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9479,8 +9454,8 @@
       </c>
     </row>
     <row r="201" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A201" s="8" t="s">
-        <v>171</v>
+      <c r="A201" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="AF201" s="2" t="str">
         <f>IF('F002'!$G104="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9516,8 +9491,8 @@
       </c>
     </row>
     <row r="202" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A202" s="8" t="s">
-        <v>172</v>
+      <c r="A202" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="AF202" s="2" t="str">
         <f>IF('F002'!$G105="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9553,8 +9528,8 @@
       </c>
     </row>
     <row r="203" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A203" s="8" t="s">
-        <v>173</v>
+      <c r="A203" s="4" t="s">
+        <v>170</v>
       </c>
       <c r="AF203" s="2" t="str">
         <f>IF('F002'!$G106="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9590,8 +9565,8 @@
       </c>
     </row>
     <row r="204" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A204" s="8" t="s">
-        <v>174</v>
+      <c r="A204" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="AF204" s="2" t="str">
         <f>IF('F002'!$G107="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9627,8 +9602,8 @@
       </c>
     </row>
     <row r="205" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A205" s="8" t="s">
-        <v>175</v>
+      <c r="A205" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="AF205" s="2" t="str">
         <f>IF('F002'!$G108="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9664,8 +9639,8 @@
       </c>
     </row>
     <row r="206" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A206" s="8" t="s">
-        <v>176</v>
+      <c r="A206" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="AF206" s="2" t="str">
         <f>IF('F002'!$G109="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9701,8 +9676,8 @@
       </c>
     </row>
     <row r="207" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A207" s="8" t="s">
-        <v>177</v>
+      <c r="A207" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="AF207" s="2" t="str">
         <f>IF('F002'!$G110="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9738,8 +9713,8 @@
       </c>
     </row>
     <row r="208" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A208" s="8" t="s">
-        <v>178</v>
+      <c r="A208" s="4" t="s">
+        <v>175</v>
       </c>
       <c r="AF208" s="2" t="str">
         <f>IF('F002'!$G111="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9775,8 +9750,8 @@
       </c>
     </row>
     <row r="209" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A209" s="8" t="s">
-        <v>179</v>
+      <c r="A209" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="AF209" s="2" t="str">
         <f>IF('F002'!$G112="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9812,8 +9787,8 @@
       </c>
     </row>
     <row r="210" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A210" s="8" t="s">
-        <v>180</v>
+      <c r="A210" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="AF210" s="2" t="str">
         <f>IF('F002'!$G113="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9849,8 +9824,8 @@
       </c>
     </row>
     <row r="211" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A211" s="8" t="s">
-        <v>181</v>
+      <c r="A211" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="AF211" s="2" t="str">
         <f>IF('F002'!$G114="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9886,8 +9861,8 @@
       </c>
     </row>
     <row r="212" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A212" s="8" t="s">
-        <v>182</v>
+      <c r="A212" s="4" t="s">
+        <v>179</v>
       </c>
       <c r="AF212" s="2" t="str">
         <f>IF('F002'!$G115="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9923,8 +9898,8 @@
       </c>
     </row>
     <row r="213" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A213" s="8" t="s">
-        <v>183</v>
+      <c r="A213" s="4" t="s">
+        <v>180</v>
       </c>
       <c r="AF213" s="2" t="str">
         <f>IF('F002'!$G116="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9960,8 +9935,8 @@
       </c>
     </row>
     <row r="214" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A214" s="8" t="s">
-        <v>184</v>
+      <c r="A214" s="4" t="s">
+        <v>181</v>
       </c>
       <c r="AF214" s="2" t="str">
         <f>IF('F002'!$G117="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -9997,8 +9972,8 @@
       </c>
     </row>
     <row r="215" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A215" s="8" t="s">
-        <v>185</v>
+      <c r="A215" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="AF215" s="2" t="str">
         <f>IF('F002'!$G118="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10034,8 +10009,8 @@
       </c>
     </row>
     <row r="216" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A216" s="8" t="s">
-        <v>186</v>
+      <c r="A216" s="4" t="s">
+        <v>183</v>
       </c>
       <c r="AF216" s="2" t="str">
         <f>IF('F002'!$G119="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10071,8 +10046,8 @@
       </c>
     </row>
     <row r="217" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A217" s="8" t="s">
-        <v>187</v>
+      <c r="A217" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="AF217" s="2" t="str">
         <f>IF('F002'!$G120="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10108,8 +10083,8 @@
       </c>
     </row>
     <row r="218" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A218" s="8" t="s">
-        <v>188</v>
+      <c r="A218" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="AF218" s="2" t="str">
         <f>IF('F002'!$G121="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10145,8 +10120,8 @@
       </c>
     </row>
     <row r="219" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A219" s="8" t="s">
-        <v>189</v>
+      <c r="A219" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="AF219" s="2" t="str">
         <f>IF('F002'!$G122="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10182,8 +10157,8 @@
       </c>
     </row>
     <row r="220" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A220" s="8" t="s">
-        <v>190</v>
+      <c r="A220" s="4" t="s">
+        <v>187</v>
       </c>
       <c r="AF220" s="2" t="str">
         <f>IF('F002'!$G123="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10219,8 +10194,8 @@
       </c>
     </row>
     <row r="221" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A221" s="8" t="s">
-        <v>191</v>
+      <c r="A221" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="AF221" s="2" t="str">
         <f>IF('F002'!$G124="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10256,8 +10231,8 @@
       </c>
     </row>
     <row r="222" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A222" s="8" t="s">
-        <v>192</v>
+      <c r="A222" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="AF222" s="2" t="str">
         <f>IF('F002'!$G125="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10293,8 +10268,8 @@
       </c>
     </row>
     <row r="223" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A223" s="8" t="s">
-        <v>193</v>
+      <c r="A223" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="AF223" s="2" t="str">
         <f>IF('F002'!$G126="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10330,8 +10305,8 @@
       </c>
     </row>
     <row r="224" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A224" s="8" t="s">
-        <v>194</v>
+      <c r="A224" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="AF224" s="2" t="str">
         <f>IF('F002'!$G127="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10367,8 +10342,8 @@
       </c>
     </row>
     <row r="225" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A225" s="8" t="s">
-        <v>195</v>
+      <c r="A225" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="AF225" s="2" t="str">
         <f>IF('F002'!$G128="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10404,8 +10379,8 @@
       </c>
     </row>
     <row r="226" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A226" s="8" t="s">
-        <v>196</v>
+      <c r="A226" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="AF226" s="2" t="str">
         <f>IF('F002'!$G129="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10441,8 +10416,8 @@
       </c>
     </row>
     <row r="227" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A227" s="8" t="s">
-        <v>197</v>
+      <c r="A227" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="AF227" s="2" t="str">
         <f>IF('F002'!$G130="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10478,8 +10453,8 @@
       </c>
     </row>
     <row r="228" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A228" s="8" t="s">
-        <v>198</v>
+      <c r="A228" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="AF228" s="2" t="str">
         <f>IF('F002'!$G131="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10515,8 +10490,8 @@
       </c>
     </row>
     <row r="229" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A229" s="8" t="s">
-        <v>199</v>
+      <c r="A229" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="AF229" s="2" t="str">
         <f>IF('F002'!$G132="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10552,8 +10527,8 @@
       </c>
     </row>
     <row r="230" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A230" s="8" t="s">
-        <v>200</v>
+      <c r="A230" s="4" t="s">
+        <v>197</v>
       </c>
       <c r="AF230" s="2" t="str">
         <f>IF('F002'!$G133="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10589,8 +10564,8 @@
       </c>
     </row>
     <row r="231" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A231" s="8" t="s">
-        <v>201</v>
+      <c r="A231" s="4" t="s">
+        <v>198</v>
       </c>
       <c r="AF231" s="2" t="str">
         <f>IF('F002'!$G134="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10626,8 +10601,8 @@
       </c>
     </row>
     <row r="232" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A232" s="8" t="s">
-        <v>202</v>
+      <c r="A232" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="AF232" s="2" t="str">
         <f>IF('F002'!$G135="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10663,8 +10638,8 @@
       </c>
     </row>
     <row r="233" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A233" s="8" t="s">
-        <v>203</v>
+      <c r="A233" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="AF233" s="2" t="str">
         <f>IF('F002'!$G136="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10700,8 +10675,8 @@
       </c>
     </row>
     <row r="234" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A234" s="8" t="s">
-        <v>204</v>
+      <c r="A234" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="AF234" s="2" t="str">
         <f>IF('F002'!$G137="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10737,8 +10712,8 @@
       </c>
     </row>
     <row r="235" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A235" s="8" t="s">
-        <v>205</v>
+      <c r="A235" s="4" t="s">
+        <v>202</v>
       </c>
       <c r="AF235" s="2" t="str">
         <f>IF('F002'!$G138="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10774,8 +10749,8 @@
       </c>
     </row>
     <row r="236" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A236" s="8" t="s">
-        <v>206</v>
+      <c r="A236" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="AF236" s="2" t="str">
         <f>IF('F002'!$G139="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10811,8 +10786,8 @@
       </c>
     </row>
     <row r="237" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A237" s="8" t="s">
-        <v>207</v>
+      <c r="A237" s="4" t="s">
+        <v>204</v>
       </c>
       <c r="AF237" s="2" t="str">
         <f>IF('F002'!$G140="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10848,8 +10823,8 @@
       </c>
     </row>
     <row r="238" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A238" s="8" t="s">
-        <v>208</v>
+      <c r="A238" s="4" t="s">
+        <v>205</v>
       </c>
       <c r="AF238" s="2" t="str">
         <f>IF('F002'!$G141="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10885,8 +10860,8 @@
       </c>
     </row>
     <row r="239" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A239" s="8" t="s">
-        <v>209</v>
+      <c r="A239" s="4" t="s">
+        <v>206</v>
       </c>
       <c r="AF239" s="2" t="str">
         <f>IF('F002'!$G142="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -10922,8 +10897,8 @@
       </c>
     </row>
     <row r="240" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A240" s="8" t="s">
-        <v>210</v>
+      <c r="A240" s="4" t="s">
+        <v>207</v>
       </c>
       <c r="AF240" s="2" t="str">
         <f>IF('F002'!$G143="NO PELIGROSO",DATOS!$AF$9,"")</f>
@@ -12360,7 +12335,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9F7948A-F2AA-4F41-AC56-ECC72F414CC8}">
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
@@ -12375,200 +12350,160 @@
     <col min="10" max="10" width="19.5703125" customWidth="1"/>
     <col min="11" max="11" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="30.140625" customWidth="1"/>
-    <col min="13" max="20" width="9.140625" style="5"/>
-    <col min="22" max="22" width="31.140625" customWidth="1"/>
-    <col min="23" max="24" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A1" s="20"/>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="24" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="24"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="25"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="25"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="37"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="37"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="26"/>
+    </row>
+    <row r="7" spans="1:12" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:12" s="2" customFormat="1" ht="43.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="21"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="22"/>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="22"/>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="22"/>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="22"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="23"/>
-    </row>
-    <row r="7" spans="1:24" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:24" s="2" customFormat="1" ht="43.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="38" t="s">
+      <c r="F8" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="L8" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>59</v>
-      </c>
-      <c r="I8" s="38" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="K8" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="L8" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="X8" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" s="2" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
-      <c r="B9" s="39"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="V9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="4" t="s">
-        <v>9</v>
-      </c>
+    </row>
+    <row r="9" spans="1:12" s="2" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="19"/>
     </row>
   </sheetData>
   <autoFilter ref="A9:L9" xr:uid="{7AE98788-07FF-4D03-BACC-51BB790DE2FF}"/>
   <mergeCells count="20">
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="C8:C9"/>
     <mergeCell ref="A1:D6"/>
     <mergeCell ref="L1:L6"/>
     <mergeCell ref="E1:K2"/>
@@ -12577,6 +12512,18 @@
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="I6:K6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -12591,15 +12538,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AA2204A4D9AA9D4B89FB124A5E810074" ma:contentTypeVersion="8" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a4c1a5ad0b74351a028e8ba01a85c73c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="9a58ed00-9ae4-408a-9b66-a7a3cce136c9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0d43c789313f3b9181b834a1eef85254" ns3:_="">
     <xsd:import namespace="9a58ed00-9ae4-408a-9b66-a7a3cce136c9"/>
@@ -12769,6 +12707,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EEB6011-5817-4697-B0FA-BBDB28BA3F0A}">
   <ds:schemaRefs>
@@ -12779,14 +12726,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BC7040B-E15D-42A0-8758-CF059F252CDE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD50DDB8-F127-4116-A4EB-E263DF3E67CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12802,4 +12741,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BC7040B-E15D-42A0-8758-CF059F252CDE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>